--- a/artifacts/SOL_USDT/metrics/SOL_USDT_metrics.xlsx
+++ b/artifacts/SOL_USDT/metrics/SOL_USDT_metrics.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>83.87914318075737</v>
+        <v>57.94609431443171</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.15855573661903</v>
+        <v>7.612233201527112</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.12894509864833</v>
+        <v>5.300704718125346</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9405151611932028</v>
+        <v>0.8895475090804614</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.720138024824021</v>
+        <v>3.563103043825965</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>165.4380821917808</v>
+        <v>151.4059060402684</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>162.5070409570908</v>
+        <v>151.5519466664827</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>171.4771900824369</v>
+        <v>150.504168416513</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>168.4821764203669</v>
+        <v>151.0607390931156</v>
       </c>
     </row>
   </sheetData>

--- a/artifacts/SOL_USDT/metrics/SOL_USDT_metrics.xlsx
+++ b/artifacts/SOL_USDT/metrics/SOL_USDT_metrics.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>57.94609431443171</v>
+        <v>82.63021983542924</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.612233201527112</v>
+        <v>9.090116601861014</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.300704718125346</v>
+        <v>7.023812664958451</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8895475090804614</v>
+        <v>0.8334834240446645</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.563103043825965</v>
+        <v>4.802323022226219</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>151.4059060402684</v>
+        <v>150.9504026845638</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>151.5519466664827</v>
+        <v>145.1911933254443</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>150.504168416513</v>
+        <v>149.6785503922859</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>151.0607390931156</v>
+        <v>144.4637826190043</v>
       </c>
     </row>
   </sheetData>
